--- a/data/ozon_content_rating.xlsx
+++ b/data/ozon_content_rating.xlsx
@@ -3575,25 +3575,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>1850</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3623,32 +3623,32 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>8850</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3678,32 +3678,32 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1850</v>
+        <v>8850</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>17</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>58850</v>
+        <v>6850</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3903,25 +3903,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>17</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>6850</v>
+        <v>58850</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3957,28 +3957,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4850</v>
+        <v>3850</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>10</v>
@@ -4003,32 +4003,32 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D67" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>3850</v>
+        <v>7850</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -4056,35 +4056,35 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>7850</v>
+        <v>4850</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>10</v>
@@ -4109,26 +4109,26 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>26</v>
       </c>
       <c r="D70" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1350</v>
+        <v>16850</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
         <v>30</v>
@@ -4223,28 +4223,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>26</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>16850</v>
+        <v>1350</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" t="n">
         <v>30</v>
@@ -4331,25 +4331,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D73" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4378,35 +4378,35 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>11850</v>
+        <v>1850</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>10</v>
@@ -4432,19 +4432,19 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -4493,25 +4493,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4540,32 +4540,32 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>1350</v>
+        <v>2850</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -4601,19 +4601,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>1350</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>10</v>
@@ -4655,25 +4655,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>11850</v>
+        <v>1850</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -4702,35 +4702,35 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D80" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1350</v>
+        <v>2350</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>10</v>
@@ -4756,26 +4756,26 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D81" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>2850</v>
+        <v>11850</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4864,32 +4864,32 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D83" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>2350</v>
+        <v>3850</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>2850</v>
+        <v>1350</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -4972,32 +4972,32 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D85" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>2850</v>
+        <v>3850</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5026,32 +5026,32 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D86" t="n">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1850</v>
+        <v>2850</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5080,35 +5080,35 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D87" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>3850</v>
+        <v>11850</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>10</v>
@@ -5134,32 +5134,32 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>3850</v>
+        <v>118850</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5188,35 +5188,35 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D89" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>10</v>
@@ -5249,25 +5249,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5296,32 +5296,32 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D91" t="n">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>950</v>
+        <v>2850</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -5350,19 +5350,19 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -5411,25 +5411,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="D93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>2350</v>
+        <v>950</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -5438,10 +5438,10 @@
         <v>10</v>
       </c>
       <c r="I93" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -5449,53 +5449,52 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Вид техники, OEM-номер, Место установки, Цвет товара</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="D94" t="n">
+        <v>17</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>6850</v>
+      </c>
+      <c r="G94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>118850</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
       <c r="H94" t="n">
         <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
@@ -5503,53 +5502,52 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D95" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>6850</v>
+        <v>9850</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -5557,40 +5555,40 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D96" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5599,10 +5597,10 @@
         <v>10</v>
       </c>
       <c r="I96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
@@ -5610,27 +5608,27 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Вид техники, OEM-номер, Место установки, Цвет товара</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -5643,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>12850</v>
+        <v>9850</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -5671,32 +5669,32 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>9850</v>
+        <v>5350</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5724,32 +5722,32 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D99" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>8850</v>
+        <v>1850</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5777,19 +5775,19 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -5802,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>8850</v>
+        <v>12850</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5830,32 +5828,32 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D101" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>1850</v>
+        <v>8850</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -5883,32 +5881,32 @@
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>8850</v>
+        <v>7850</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -5943,28 +5941,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D103" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>2850</v>
+        <v>3850</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -5989,32 +5987,32 @@
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>9850</v>
+        <v>8850</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6049,25 +6047,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D105" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6095,32 +6093,32 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>9850</v>
+        <v>950</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6148,32 +6146,32 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>8850</v>
+        <v>2850</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -6208,28 +6206,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D108" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>5350</v>
+        <v>1850</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
         <v>10</v>
@@ -6254,32 +6252,32 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D109" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>7850</v>
+        <v>9850</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -6314,28 +6312,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D110" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>3850</v>
+        <v>950</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>10</v>
@@ -6344,7 +6342,7 @@
         <v>100</v>
       </c>
       <c r="J110" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
@@ -6354,13 +6352,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -6630,7 +6628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -6692,7 +6690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -6702,13 +6700,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Комплектация</t>
+          <t>Материал</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6718,11 +6716,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Комплектация</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
@@ -6752,27 +6750,27 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Количество в упаковке, шт</t>
+          <t>Расположение детали</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Расположение детали</t>
+          <t>Количество в упаковке, шт</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25">
@@ -6828,7 +6826,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>#Хештеги</t>
+          <t>Rich-контент JSON</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6838,7 +6836,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rich-контент JSON</t>
+          <t>#Хештеги</t>
         </is>
       </c>
       <c r="B31" t="n">

--- a/data/ozon_content_rating.xlsx
+++ b/data/ozon_content_rating.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44</v>
+        <v>51.5</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
@@ -554,7 +554,7 @@
         <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -563,14 +563,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -586,7 +585,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24.5</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
         <v>17</v>
@@ -607,7 +606,7 @@
         <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -617,13 +616,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -639,7 +638,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>26</v>
+        <v>33.5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -660,7 +659,7 @@
         <v>50</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -670,14 +669,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -693,7 +691,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -714,7 +712,7 @@
         <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -724,14 +722,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -747,7 +744,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -768,7 +765,7 @@
         <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -779,12 +776,12 @@
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON</t>
         </is>
       </c>
     </row>
@@ -800,7 +797,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -821,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -831,14 +828,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -892,7 +888,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -908,7 +904,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>177</v>
@@ -929,7 +925,7 @@
         <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -939,14 +935,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -962,7 +957,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>47.5</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
         <v>42</v>
@@ -983,7 +978,7 @@
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -992,14 +987,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1062,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D12" t="n">
         <v>151</v>
@@ -1089,7 +1083,7 @@
         <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -1099,14 +1093,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1151,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Комплектация, Материал, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1167,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>24.5</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
         <v>34</v>
@@ -1195,7 +1188,7 @@
         <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -1205,13 +1198,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Материал, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1220,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>95</v>
@@ -1248,7 +1241,7 @@
         <v>100</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -1258,14 +1251,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1273,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D16" t="n">
         <v>24</v>
@@ -1302,7 +1294,7 @@
         <v>100</v>
       </c>
       <c r="J16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -1312,13 +1304,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, Внутренний диаметр, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1326,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>24.5</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>122</v>
@@ -1355,7 +1347,7 @@
         <v>50</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -1365,13 +1357,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Материал, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1379,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -1408,7 +1400,7 @@
         <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -1418,14 +1410,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1432,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D19" t="n">
         <v>122</v>
@@ -1462,7 +1453,7 @@
         <v>50</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -1472,14 +1463,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1485,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>38.5</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
         <v>61</v>
@@ -1516,7 +1506,7 @@
         <v>100</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -1526,14 +1516,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1538,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>191</v>
@@ -1570,7 +1559,7 @@
         <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -1579,13 +1568,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Rich-контент JSON, Материал, Внутренний диаметр, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1590,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="D22" t="n">
         <v>75</v>
@@ -1622,7 +1611,7 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -1632,12 +1621,12 @@
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1642,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D23" t="n">
         <v>75</v>
@@ -1674,7 +1663,7 @@
         <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -1684,13 +1673,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1695,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D24" t="n">
         <v>137</v>
@@ -1727,7 +1716,7 @@
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
@@ -1737,14 +1726,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1748,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D25" t="n">
         <v>151</v>
@@ -1781,7 +1769,7 @@
         <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -1791,14 +1779,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1801,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D26" t="n">
         <v>149</v>
@@ -1835,7 +1822,7 @@
         <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -1845,14 +1832,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1891,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1945,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1961,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1996,7 +1982,7 @@
         <v>50</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -2006,14 +1992,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2014,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D30" t="n">
         <v>31</v>
@@ -2050,7 +2035,7 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
@@ -2060,14 +2045,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2067,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
         <v>141</v>
@@ -2104,7 +2088,7 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -2114,14 +2098,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2120,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D32" t="n">
         <v>261</v>
@@ -2158,7 +2141,7 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -2168,14 +2151,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2173,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>24.5</v>
+        <v>47</v>
       </c>
       <c r="D33" t="n">
         <v>151</v>
@@ -2212,7 +2194,7 @@
         <v>50</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -2222,13 +2204,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
-Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON</t>
         </is>
       </c>
     </row>
@@ -2243,8 +2225,8 @@
           <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>50</v>
+      <c r="C34" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D34" t="n">
         <v>229</v>
@@ -2265,7 +2247,7 @@
         <v>50</v>
       </c>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -2275,12 +2257,12 @@
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Rich-контент JSON, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Rich-контент JSON</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2332,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D36" t="n">
         <v>109</v>
@@ -2371,7 +2353,7 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -2381,14 +2363,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2422,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2438,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D38" t="n">
         <v>20</v>
@@ -2478,7 +2459,7 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -2488,14 +2469,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2529,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2545,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>35</v>
+        <v>42.5</v>
       </c>
       <c r="D40" t="n">
         <v>21</v>
@@ -2586,7 +2566,7 @@
         <v>50</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -2595,14 +2575,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2634,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2705,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>35</v>
+        <v>42.5</v>
       </c>
       <c r="D43" t="n">
         <v>156</v>
@@ -2747,7 +2726,7 @@
         <v>50</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -2756,14 +2735,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2757,7 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D44" t="n">
         <v>206</v>
@@ -2800,7 +2778,7 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -2810,14 +2788,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2847,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2863,7 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
         <v>108</v>
@@ -2907,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -2918,14 +2895,13 @@
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2917,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D47" t="n">
         <v>42</v>
@@ -2962,7 +2938,7 @@
         <v>50</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -2972,14 +2948,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2970,7 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D48" t="n">
         <v>75</v>
@@ -3016,7 +2991,7 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -3026,14 +3001,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3023,7 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D49" t="n">
         <v>35</v>
@@ -3070,7 +3044,7 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -3080,14 +3054,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3129,7 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D51" t="n">
         <v>46</v>
@@ -3177,7 +3150,7 @@
         <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -3187,14 +3160,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3182,7 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D52" t="n">
         <v>8</v>
@@ -3231,7 +3203,7 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -3241,14 +3213,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3272,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3341,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>47.5</v>
+        <v>55</v>
       </c>
       <c r="D55" t="n">
         <v>33</v>
@@ -3391,7 +3362,7 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -3400,14 +3371,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3393,7 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D56" t="n">
         <v>65</v>
@@ -3444,7 +3414,7 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -3454,14 +3424,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3446,7 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D57" t="n">
         <v>74</v>
@@ -3498,7 +3467,7 @@
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -3508,14 +3477,13 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3499,7 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D58" t="n">
         <v>51</v>
@@ -3552,7 +3520,7 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -3562,38 +3530,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="D59" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>1850</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3623,32 +3591,32 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>1850</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3660,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -3671,14 +3639,13 @@
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3661,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>25</v>
@@ -3715,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -3726,14 +3693,13 @@
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Аннотация, Rich-контент JSON, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -3795,25 +3761,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>58850</v>
+        <v>4850</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3825,7 +3791,7 @@
         <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -3835,42 +3801,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>6850</v>
+        <v>3850</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>10</v>
@@ -3879,7 +3844,7 @@
         <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -3889,42 +3854,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>58850</v>
+        <v>7850</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>10</v>
@@ -3933,7 +3897,7 @@
         <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -3943,42 +3907,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>3850</v>
+        <v>6850</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>10</v>
@@ -4003,35 +3966,35 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>7850</v>
+        <v>58850</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>10</v>
@@ -4056,35 +4019,35 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>4850</v>
+        <v>7850</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>10</v>
@@ -4109,35 +4072,35 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>7850</v>
+        <v>58850</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>10</v>
@@ -4162,7 +4125,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -4216,41 +4179,41 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>26</v>
+        <v>29.5</v>
       </c>
       <c r="D71" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>1350</v>
+        <v>2850</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I71" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4258,10 +4221,10 @@
       <c r="K71" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 1 до 2 изображений (+10)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Медиа: Добавлено от 3 до 4 изображений (+30)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
@@ -4270,41 +4233,41 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>26</v>
+        <v>29.5</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>58850</v>
+        <v>1350</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4312,10 +4275,10 @@
       <c r="K72" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 1 до 2 изображений (+10)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Медиа: Добавлено от 3 до 4 изображений (+30)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
@@ -4324,32 +4287,32 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Цвет товара, Альтернативные артикулы товара</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D73" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>2350</v>
+        <v>1350</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4378,32 +4341,32 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D74" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>1850</v>
+        <v>3850</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4432,19 +4395,19 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -4493,25 +4456,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D76" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1350</v>
+        <v>3850</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4540,19 +4503,19 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -4565,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>2850</v>
+        <v>11850</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>10</v>
@@ -4594,26 +4557,26 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D78" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -4622,7 +4585,7 @@
         <v>1350</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>10</v>
@@ -4655,37 +4618,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>1850</v>
+        <v>6850</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>10</v>
       </c>
       <c r="I79" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -4693,95 +4656,93 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
 Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>29.5</v>
+        <v>33.5</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>2350</v>
+        <v>1350</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I80" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 3 до 4 изображений (+30)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Медиа: Добавлено от 1 до 2 изображений (+10)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Текстовое описание: Заполнен Rich-контент (+50)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D81" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1350</v>
+        <v>2850</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -4793,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -4803,30 +4764,29 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -4835,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>11850</v>
+        <v>12850</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4847,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
@@ -4857,39 +4817,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>3850</v>
+        <v>950</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4901,7 +4860,7 @@
         <v>100</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -4911,39 +4870,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1350</v>
+        <v>2350</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -4955,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
@@ -4965,39 +4923,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D85" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>3850</v>
+        <v>5350</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5009,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -5019,39 +4976,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D86" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5063,7 +5019,7 @@
         <v>100</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
@@ -5073,39 +5029,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>11850</v>
+        <v>1850</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -5117,7 +5072,7 @@
         <v>100</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -5127,39 +5082,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>118850</v>
+        <v>1850</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5171,7 +5125,7 @@
         <v>100</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
@@ -5181,39 +5135,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D89" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1350</v>
+        <v>118850</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5225,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -5235,39 +5188,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D90" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>950</v>
+        <v>1850</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5279,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
@@ -5289,42 +5241,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2850</v>
+        <v>1350</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>10</v>
@@ -5333,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -5343,39 +5294,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Количество, штук, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>29.5</v>
+        <v>37</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>1350</v>
+        <v>2850</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -5387,7 +5337,7 @@
         <v>100</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
@@ -5397,51 +5347,50 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D93" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>950</v>
+        <v>3850</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>10</v>
       </c>
       <c r="I93" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -5449,52 +5398,52 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Вид техники, OEM-номер, Место установки, Цвет товара</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>6850</v>
+        <v>2350</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
@@ -5502,40 +5451,40 @@
 Медиа: Добавлено от 3 до 4 изображений (+30)
 Медиа: Добавлено от 5 до 7 изображений (+50)
 Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>9850</v>
+        <v>1350</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -5563,32 +5512,32 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>8850</v>
+        <v>11850</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5616,32 +5565,32 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>9850</v>
+        <v>1350</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -5669,85 +5618,85 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D98" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>5350</v>
+        <v>58850</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 3 до 4 изображений (+30)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Медиа: Добавлено от 1 до 2 изображений (+10)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Материал, OEM-номер, Внутренний диаметр, мм, Цвет товара, Альтернативные артикулы товара</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D99" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1850</v>
+        <v>7850</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5759,7 +5708,7 @@
         <v>100</v>
       </c>
       <c r="J99" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -5769,38 +5718,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>12850</v>
+        <v>950</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5812,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="J100" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
@@ -5822,32 +5771,32 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -5865,7 +5814,7 @@
         <v>100</v>
       </c>
       <c r="J101" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -5875,38 +5824,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D102" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>7850</v>
+        <v>2850</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -5918,7 +5867,7 @@
         <v>100</v>
       </c>
       <c r="J102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
@@ -5928,41 +5877,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D103" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>3850</v>
+        <v>8850</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -5971,7 +5920,7 @@
         <v>100</v>
       </c>
       <c r="J103" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -5981,32 +5930,32 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D104" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -6024,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="J104" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
@@ -6034,29 +5983,29 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D105" t="n">
         <v>8</v>
@@ -6065,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>8850</v>
+        <v>9850</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6077,7 +6026,7 @@
         <v>100</v>
       </c>
       <c r="J105" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -6087,38 +6036,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D106" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6130,7 +6079,7 @@
         <v>100</v>
       </c>
       <c r="J106" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
@@ -6140,38 +6089,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D107" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>2850</v>
+        <v>9850</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -6183,7 +6132,7 @@
         <v>100</v>
       </c>
       <c r="J107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -6193,41 +6142,41 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D108" t="n">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>10</v>
@@ -6236,7 +6185,7 @@
         <v>100</v>
       </c>
       <c r="J108" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
@@ -6246,32 +6195,32 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>37</v>
+        <v>44.5</v>
       </c>
       <c r="D109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -6289,7 +6238,7 @@
         <v>100</v>
       </c>
       <c r="J109" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -6299,38 +6248,38 @@
 Медиа: Добавлено от 8 изображений (+60)
 Текстовое описание: Аннотация более 500 знаков (+50)
 Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D110" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -6358,19 +6307,19 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -6383,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>8850</v>
+        <v>7850</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -6411,113 +6360,113 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>44.5</v>
+        <v>46</v>
       </c>
       <c r="D112" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>7850</v>
+        <v>4850</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I112" t="n">
         <v>100</v>
       </c>
       <c r="J112" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 3 до 4 изображений (+30)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Медиа: Добавлено от 1 до 2 изображений (+10)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 500 знаков (+50)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
 Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D113" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>4850</v>
+        <v>950</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I113" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J113" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
           <t>Медиа: Добавлена видео или видеообложка (+40)
-Медиа: Добавлено от 1 до 2 изображений (+10)
-Медиа: Добавлено от 5 до 7 изображений (+50)
-Медиа: Добавлено от 8 изображений (+60)
-Текстовое описание: Аннотация более 500 знаков (+50)
-Текстовое описание: Заполнен Rich-контент (+50)
-Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)
-Остальные атрибуты: Заполнено от 70% атрибутов (+100)</t>
+Медиа: Добавлено от 3 до 4 изображений (+30)
+Медиа: Добавлено от 5 до 7 изображений (+50)
+Медиа: Добавлено от 8 изображений (+60)
+Текстовое описание: Аннотация более 100 знаков и до 500 (+100)
+Текстовое описание: Заполнен Rich-контент (+50)
+Остальные атрибуты: Заполнено от 15% до 50% атрибутов (+25)
+Остальные атрибуты: Заполнено от 50% до 70% атрибутов (+50)</t>
         </is>
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -6588,67 +6537,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Остальные атрибуты: Заполнено от 50% до 70% атрибутов</t>
+          <t>Медиа: Добавлена видео или видеообложка</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Медиа: Добавлена видео или видеообложка</t>
+          <t>Медиа: Добавлено от 3 до 4 изображений</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Медиа: Добавлено от 3 до 4 изображений</t>
+          <t>Остальные атрибуты: Заполнено от 50% до 70% атрибутов</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Остальные атрибуты: Заполнено от 15% до 50% атрибутов</t>
+          <t>Текстовое описание: Аннотация более 500 знаков</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Текстовое описание: Аннотация более 500 знаков</t>
+          <t>Текстовое описание: Аннотация более 100 знаков и до 500</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Текстовое описание: Аннотация более 100 знаков и до 500</t>
+          <t>Остальные атрибуты: Заполнено от 15% до 50% атрибутов</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6686,177 +6635,177 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Вид техники</t>
+          <t>Материал</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OEM-номер</t>
+          <t>Озон.Видео: ссылка</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Озон.Видеообложка: ссылка</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Комплектация</t>
+          <t>Внутренний диаметр, мм</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Озон.Видео: ссылка</t>
+          <t>Расположение детали</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Озон.Видеообложка: ссылка</t>
+          <t>Высота, мм</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Внутренний диаметр, мм</t>
+          <t>Ширина, мм</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Расположение детали</t>
+          <t>Длина, мм</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Количество в упаковке, шт</t>
+          <t>Цвет товара</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Высота, мм</t>
+          <t>Альтернативные артикулы товара</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ширина, мм</t>
+          <t>OEM-номер</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Длина, мм</t>
+          <t>#Хештеги</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Альтернативные артикулы товара</t>
+          <t>Rich-контент JSON</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Цвет товара</t>
+          <t>Комплектация</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rich-контент JSON</t>
+          <t>Количество в упаковке, шт</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>#Хештеги</t>
+          <t>Вид техники</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Количество, штук</t>
+          <t>Форма</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Форма</t>
+          <t>Исполнение фильтра</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6866,7 +6815,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Исполнение фильтра</t>
+          <t>Корпус фильтра</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6876,11 +6825,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Корпус фильтра</t>
+          <t>Аннотация</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -6890,23 +6839,23 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Аннотация</t>
+          <t>Внешний диаметр, мм</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Внешний диаметр, мм</t>
+          <t>Вид подшипников</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6916,7 +6865,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Вид подшипников</t>
+          <t>Вид запчасти</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6926,21 +6875,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Вид запчасти</t>
+          <t>Количество, штук</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Место установки</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/ozon_content_rating.xlsx
+++ b/data/ozon_content_rating.xlsx
@@ -3761,28 +3761,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>4850</v>
+        <v>7850</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>10</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
@@ -3867,28 +3867,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>7850</v>
+        <v>58850</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -3973,28 +3973,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>58850</v>
+        <v>7850</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>10</v>
@@ -4019,35 +4019,35 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Вид техники, OEM-номер, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>7850</v>
+        <v>58850</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>10</v>
@@ -4072,32 +4072,32 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>24.5</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>58850</v>
+        <v>4850</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Rich-контент JSON, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
@@ -4240,25 +4240,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1350</v>
+        <v>3850</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4287,19 +4287,19 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4402,12 +4402,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -4456,25 +4456,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>3850</v>
+        <v>1350</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4503,35 +4503,35 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>11850</v>
+        <v>1350</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>10</v>
@@ -4557,35 +4557,35 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>29.5</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1350</v>
+        <v>11850</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Высота, мм, Материал, Вид техники, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, Вид техники, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Ширина, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
@@ -4777,25 +4777,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>12850</v>
+        <v>1850</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D83" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4883,25 +4883,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>2350</v>
+        <v>1850</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -4929,35 +4929,35 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D85" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>5350</v>
+        <v>3850</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>10</v>
@@ -4982,32 +4982,32 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D86" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1850</v>
+        <v>2850</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5035,35 +5035,35 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D87" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>10</v>
@@ -5088,32 +5088,32 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D88" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5141,32 +5141,32 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>118850</v>
+        <v>2350</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5194,32 +5194,32 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D90" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5247,35 +5247,35 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D91" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1350</v>
+        <v>5350</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>10</v>
@@ -5300,35 +5300,35 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Ширина, мм, Высота, мм, Материал, Единиц в одном товаре, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D92" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>10</v>
@@ -5353,35 +5353,35 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D93" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>3850</v>
+        <v>1850</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>10</v>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D94" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2350</v>
+        <v>11850</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5459,32 +5459,32 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Ширина, мм, Высота, мм, Материал, OEM-номер, Длина, мм, Форма, Исполнение фильтра, Корпус фильтра, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1350</v>
+        <v>12850</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -5512,32 +5512,32 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, OEM-номер, Внутренний диаметр, мм, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внешний диаметр, мм, Внутренний диаметр, мм, Высота, мм, Цвет товара, Вид подшипников, #Хештеги, Вид запчасти</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>11850</v>
+        <v>118850</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5572,19 +5572,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>37</v>
       </c>
       <c r="D97" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
         <v>1350</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>10</v>
@@ -5678,19 +5678,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D99" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5724,32 +5724,32 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D100" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5777,32 +5777,32 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D101" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>8850</v>
+        <v>9850</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -5830,32 +5830,32 @@
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D102" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>2850</v>
+        <v>9850</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -5883,26 +5883,26 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -5943,25 +5943,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D104" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>8850</v>
+        <v>950</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -5989,32 +5989,32 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, OEM-номер, Внутренний диаметр, мм, Альтернативные артикулы товара, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>9850</v>
+        <v>8850</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6042,32 +6042,32 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>8850</v>
+        <v>7850</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6155,25 +6155,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D108" t="n">
-        <v>215</v>
+        <v>30</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>950</v>
+        <v>8850</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -6201,32 +6201,32 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>9850</v>
+        <v>2850</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали, #Хештеги</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Материал, OEM-номер, Внутренний диаметр, мм, Расположение детали, #Хештеги</t>
         </is>
       </c>
     </row>
@@ -6314,25 +6314,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>44.5</v>
       </c>
       <c r="D111" t="n">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>7850</v>
+        <v>950</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Комплектация, Материал, OEM-номер, Внутренний диаметр, мм, Количество в упаковке, шт, Расположение детали</t>
+          <t>Изображения, Озон.Видео: ссылка, Озон.Видеообложка: ссылка, Высота, мм, Материал, Ширина, мм, Длина, мм, Цвет товара, Альтернативные артикулы товара, Расположение детали</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Внешний диаметр, мм</t>
+          <t>Количество, штук</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6855,7 +6855,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Вид подшипников</t>
+          <t>Внешний диаметр, мм</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6865,7 +6865,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Вид запчасти</t>
+          <t>Вид подшипников</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6875,7 +6875,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Количество, штук</t>
+          <t>Вид запчасти</t>
         </is>
       </c>
       <c r="B40" t="n">
